--- a/artfynd/A 59039-2022 artfynd.xlsx
+++ b/artfynd/A 59039-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59039-2022 artfynd.xlsx
+++ b/artfynd/A 59039-2022 artfynd.xlsx
@@ -1258,7 +1258,7 @@
         <v>117316431</v>
       </c>
       <c r="B7" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 59039-2022 artfynd.xlsx
+++ b/artfynd/A 59039-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56218747</v>
+        <v>56218746</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473455.9992731893</v>
+        <v>473455</v>
       </c>
       <c r="R2" t="n">
-        <v>7087502.207017551</v>
+        <v>7087500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56218746</v>
+        <v>56218751</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473455.099149387</v>
+        <v>473460</v>
       </c>
       <c r="R3" t="n">
-        <v>7087500.013714396</v>
+        <v>7087539</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56218748</v>
+        <v>56218749</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473434.6463805898</v>
+        <v>473452</v>
       </c>
       <c r="R4" t="n">
-        <v>7087531.000229144</v>
+        <v>7087568</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,37 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56218749</v>
+        <v>56218748</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473452.1482786415</v>
+        <v>473435</v>
       </c>
       <c r="R5" t="n">
-        <v>7087567.826901498</v>
+        <v>7087531</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56218751</v>
+        <v>56218747</v>
       </c>
       <c r="B6" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473460.2793557015</v>
+        <v>473456</v>
       </c>
       <c r="R6" t="n">
-        <v>7087539.146234998</v>
+        <v>7087502</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2013-11-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-11-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,12 +1183,7 @@
         <v>117316431</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 59039-2022 artfynd.xlsx
+++ b/artfynd/A 59039-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218746</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218749</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218748</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218747</t>
         </is>
       </c>
     </row>
@@ -1283,8 +1313,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117316431</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>